--- a/data/Terre di Pedemonte/investment_decision/Tegna_SFH_until_2004_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Tegna_SFH_until_2004_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>193.0105997982729</v>
+        <v>107.4456026178339</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>128349.1495913751</v>
       </c>
       <c r="F2" t="n">
-        <v>193.0105997982729</v>
+        <v>107.4456026178338</v>
       </c>
       <c r="G2" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="H2" t="n">
-        <v>193.0105997982729</v>
+        <v>107.4456026178339</v>
       </c>
       <c r="I2" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="J2" t="n">
-        <v>193.0105997982729</v>
+        <v>107.4456026178339</v>
       </c>
       <c r="K2" t="n">
         <v>128349.1495913751</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>587.6720285916316</v>
+        <v>230.8252476624497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>128349.1495913751</v>
       </c>
       <c r="F3" t="n">
-        <v>579.3549689827122</v>
+        <v>243.8294099792446</v>
       </c>
       <c r="G3" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="H3" t="n">
-        <v>706.5753230984475</v>
+        <v>195.5121757855476</v>
       </c>
       <c r="I3" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="J3" t="n">
-        <v>676.0821947986211</v>
+        <v>238.5824542832544</v>
       </c>
       <c r="K3" t="n">
         <v>128349.1495913751</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>687.9241099750946</v>
+        <v>542.0850953158092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>128349.1495913751</v>
       </c>
       <c r="F4" t="n">
-        <v>640.1949219058674</v>
+        <v>542.0850953158089</v>
       </c>
       <c r="G4" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="H4" t="n">
-        <v>753.5865823682715</v>
+        <v>542.085095315809</v>
       </c>
       <c r="I4" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="J4" t="n">
-        <v>676.0821947986211</v>
+        <v>541.4109320325314</v>
       </c>
       <c r="K4" t="n">
         <v>128349.1495913751</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>899.9506008955866</v>
+        <v>594.416695185882</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>128349.1495913751</v>
       </c>
       <c r="F5" t="n">
-        <v>705.9734356163131</v>
+        <v>594.4166951858824</v>
       </c>
       <c r="G5" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="H5" t="n">
-        <v>882.0722294930322</v>
+        <v>595.4138313702338</v>
       </c>
       <c r="I5" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="J5" t="n">
-        <v>676.0821947986211</v>
+        <v>594.6601109008142</v>
       </c>
       <c r="K5" t="n">
         <v>128349.1495913751</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>899.9506008955865</v>
+        <v>594.416695185882</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>128349.1495913751</v>
       </c>
       <c r="F6" t="n">
-        <v>705.9734356163131</v>
+        <v>594.4166951858824</v>
       </c>
       <c r="G6" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="H6" t="n">
-        <v>882.0722294930322</v>
+        <v>595.4138313702338</v>
       </c>
       <c r="I6" t="n">
         <v>128349.1495913751</v>
       </c>
       <c r="J6" t="n">
-        <v>676.0821947986211</v>
+        <v>594.6601109008142</v>
       </c>
       <c r="K6" t="n">
         <v>128349.1495913751</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>192.5237243870626</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>109.6344617202624</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>192.5237243870626</v>
+        <v>123.4080577835528</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>109.6344617202624</v>
+        <v>123.4080577835528</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>192.5237243870626</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>133.4562926923188</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>192.5237243870626</v>
+        <v>150.2226728870649</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>133.4562926923188</v>
+        <v>150.2226728870649</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>192.5237243870626</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>143.2144330627256</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>192.5237243870626</v>
+        <v>161.206747892275</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>143.2144330627256</v>
+        <v>161.206747892275</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>192.5237243870626</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>148.430605652924</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>192.5237243870626</v>
+        <v>167.0782386472773</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>148.430605652924</v>
+        <v>167.0782386472773</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>192.5237243870626</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>151.6900409227308</v>
+        <v>216.7108638202247</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>192.5237243870626</v>
+        <v>170.7471632701245</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>151.6900409227308</v>
+        <v>170.7471632701245</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.02917401712941177</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.02917401712941177</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.02917401712941177</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.02917401712941177</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.03063271798588235</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.03063271798588235</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.03063271798588235</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.03109486368393528</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03355011969882347</v>
+        <v>0.03063271798588235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03355011969882387</v>
+        <v>0.03063271798588235</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03355011969882353</v>
+        <v>0.03063271798588235</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03355011969882352</v>
+        <v>0.03109486368393528</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03646752141176471</v>
+        <v>0.03355011969882353</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03646752141176471</v>
+        <v>0.03355011969882353</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03646752141176471</v>
+        <v>0.0329387230117647</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03646752141176471</v>
+        <v>0.03340086870981763</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.03646752141176471</v>
+        <v>0.03355011969882353</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03646752141176431</v>
+        <v>0.03355011969882353</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03646752141176471</v>
+        <v>0.0329387230117647</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03646752141176471</v>
+        <v>0.03340086870981763</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>1.549869659999998</v>
+        <v>5.7493483</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>26.037810288</v>
       </c>
       <c r="F19" t="n">
-        <v>1.549869660000213</v>
+        <v>5.7493483</v>
       </c>
       <c r="G19" t="n">
         <v>26.037810288</v>
       </c>
       <c r="H19" t="n">
-        <v>1.549869659999998</v>
+        <v>4.664354261183901</v>
       </c>
       <c r="I19" t="n">
         <v>26.037810288</v>
       </c>
       <c r="J19" t="n">
-        <v>1.549869659999998</v>
+        <v>4.95286092600885</v>
       </c>
       <c r="K19" t="n">
         <v>26.037810288</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>1.549869659999998</v>
+        <v>6.974413469999998</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>26.037810288</v>
       </c>
       <c r="F20" t="n">
-        <v>1.549869660000213</v>
+        <v>6.974413469999998</v>
       </c>
       <c r="G20" t="n">
         <v>26.037810288</v>
       </c>
       <c r="H20" t="n">
-        <v>1.549869659999998</v>
+        <v>4.664354261183901</v>
       </c>
       <c r="I20" t="n">
         <v>26.037810288</v>
       </c>
       <c r="J20" t="n">
-        <v>1.549869659999998</v>
+        <v>4.95286092600885</v>
       </c>
       <c r="K20" t="n">
         <v>26.037810288</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>1.549869659999998</v>
+        <v>6.974413469999998</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>26.037810288</v>
       </c>
       <c r="F21" t="n">
-        <v>1.549869660000213</v>
+        <v>6.974413469999998</v>
       </c>
       <c r="G21" t="n">
         <v>26.037810288</v>
       </c>
       <c r="H21" t="n">
-        <v>1.549869659999998</v>
+        <v>4.664354261183901</v>
       </c>
       <c r="I21" t="n">
         <v>26.037810288</v>
       </c>
       <c r="J21" t="n">
-        <v>1.549869659999998</v>
+        <v>4.95286092600885</v>
       </c>
       <c r="K21" t="n">
         <v>26.037810288</v>
@@ -1514,13 +1514,13 @@
         <v>26.037810288</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.3248044900000021</v>
       </c>
       <c r="I29" t="n">
         <v>26.037810288</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.07928958790938445</v>
       </c>
       <c r="K29" t="n">
         <v>26.037810288</v>
@@ -1551,13 +1551,13 @@
         <v>26.037810288</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.3248044900000021</v>
       </c>
       <c r="I30" t="n">
         <v>26.037810288</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.07928958790938445</v>
       </c>
       <c r="K30" t="n">
         <v>26.037810288</v>
@@ -1588,13 +1588,13 @@
         <v>26.037810288</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.3808461895316783</v>
       </c>
       <c r="I31" t="n">
         <v>26.037810288</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2000200433804637</v>
       </c>
       <c r="K31" t="n">
         <v>26.037810288</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>327.4551667027214</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>189.8666814833258</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>327.4551667027214</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>327.4551667027214</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>230.8471512221094</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>327.4551667027214</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>327.4551667027214</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>247.7240558595934</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>327.4551667027214</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>327.4551667027214</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>256.8727157773787</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>327.4551667027214</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>327.4551667027214</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>262.686711896108</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>327.4551667027214</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2362,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>55.82846487290286</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>177.9365297650131</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>23.92921265274253</v>
+        <v>16.17144724558236</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F53" t="n">
-        <v>23.7099315063884</v>
+        <v>13.58088780751012</v>
       </c>
       <c r="G53" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H53" t="n">
+        <v>15.27038655006848</v>
+      </c>
+      <c r="I53" t="n">
         <v>73.4414046231378</v>
       </c>
-      <c r="H53" t="n">
-        <v>21.306345862151</v>
-      </c>
-      <c r="I53" t="n">
-        <v>177.9365297650131</v>
-      </c>
       <c r="J53" t="n">
-        <v>20.04192762653226</v>
+        <v>12.71348590850159</v>
       </c>
       <c r="K53" t="n">
         <v>73.4414046231378</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>56.16935437220825</v>
+        <v>55.49272558880437</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F54" t="n">
-        <v>56.32263886322271</v>
+        <v>51.0075748663112</v>
       </c>
       <c r="G54" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H54" t="n">
+        <v>55.23615832600009</v>
+      </c>
+      <c r="I54" t="n">
         <v>81.29059739115766</v>
       </c>
-      <c r="H54" t="n">
-        <v>53.62439864071778</v>
-      </c>
-      <c r="I54" t="n">
-        <v>177.9365297650131</v>
-      </c>
       <c r="J54" t="n">
-        <v>51.64424363180219</v>
+        <v>50.11783183130677</v>
       </c>
       <c r="K54" t="n">
         <v>81.29059739115766</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>57.56031658341327</v>
+        <v>56.24485807628897</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F55" t="n">
-        <v>57.35762150438921</v>
+        <v>53.15906036808071</v>
       </c>
       <c r="G55" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H55" t="n">
+        <v>55.36562695234014</v>
+      </c>
+      <c r="I55" t="n">
         <v>85.52663628655606</v>
       </c>
-      <c r="H55" t="n">
-        <v>55.29262439798555</v>
-      </c>
-      <c r="I55" t="n">
-        <v>177.9365297650131</v>
-      </c>
       <c r="J55" t="n">
-        <v>53.26799089138726</v>
+        <v>52.89610943616989</v>
       </c>
       <c r="K55" t="n">
         <v>85.52663628655606</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>56.12762421131505</v>
+        <v>56.09964214562604</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F56" t="n">
-        <v>55.13836800801745</v>
+        <v>52.39630949958092</v>
       </c>
       <c r="G56" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55.79391417743545</v>
+      </c>
+      <c r="I56" t="n">
         <v>88.1415702221687</v>
       </c>
-      <c r="H56" t="n">
-        <v>53.33043839818904</v>
-      </c>
-      <c r="I56" t="n">
-        <v>177.9365297650131</v>
-      </c>
       <c r="J56" t="n">
-        <v>52.20742743031471</v>
+        <v>52.40685958486714</v>
       </c>
       <c r="K56" t="n">
         <v>88.1415702221687</v>
@@ -2547,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>55.82846487290286</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>177.9365297650131</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>73.4414046231378</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>177.9365297650131</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>81.29059739115766</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>177.9365297650131</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>85.52663628655606</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>177.9365297650131</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>177.9365297650131</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>88.1415702221687</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>177.9365297650131</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2778,7 +2778,7 @@
         <v>177.9365297650131</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2723925225850671</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>177.9365297650131</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>27.54841530884027</v>
+        <v>7.41856042609612</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F64" t="n">
-        <v>28.04523485809609</v>
+        <v>11.13366977762849</v>
       </c>
       <c r="G64" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="H64" t="n">
-        <v>28.64493414930474</v>
+        <v>6.774066993386509</v>
       </c>
       <c r="I64" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="J64" t="n">
-        <v>30.67007651731513</v>
+        <v>11.14710321730942</v>
       </c>
       <c r="K64" t="n">
         <v>177.9365297650131</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>32.48039815085966</v>
+        <v>15.95282161182836</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F65" t="n">
-        <v>36.55925559096388</v>
+        <v>18.26857794907583</v>
       </c>
       <c r="G65" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="H65" t="n">
-        <v>35.14246617604961</v>
+        <v>15.95624838692944</v>
       </c>
       <c r="I65" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="J65" t="n">
-        <v>40.04632925773006</v>
+        <v>17.68269568167273</v>
       </c>
       <c r="K65" t="n">
         <v>177.9365297650131</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>42.7305156343589</v>
+        <v>16.0980375424913</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F66" t="n">
-        <v>47.99867989528753</v>
+        <v>19.8013701885364</v>
       </c>
       <c r="G66" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="H66" t="n">
-        <v>45.92207728724714</v>
+        <v>16.429021857348</v>
       </c>
       <c r="I66" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="J66" t="n">
-        <v>51.5889860792629</v>
+        <v>19.7969855516381</v>
       </c>
       <c r="K66" t="n">
         <v>177.9365297650131</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>5.50696331159261</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>5.50696331159261</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="73">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>8.528921416565359</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>8.528921416565359</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="74">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>10.52119561557815</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>10.52119561557815</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="75">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>11.97193061940716</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>11.97193061940716</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="76">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>13.09491170153377</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>13.09491170153377</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="77">
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>5.50696331159261</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>5.50696331159261</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="78">
@@ -3321,22 +3321,22 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4027456965508756</v>
+        <v>0.770041370960776</v>
       </c>
       <c r="G78" t="n">
-        <v>8.528921416565359</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.9010606955138831</v>
       </c>
       <c r="I78" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="J78" t="n">
-        <v>1.664668249059251</v>
+        <v>1.625040018662643</v>
       </c>
       <c r="K78" t="n">
-        <v>8.528921416565359</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="79">
@@ -3358,22 +3358,22 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4027456965508756</v>
+        <v>0.770041370960776</v>
       </c>
       <c r="G79" t="n">
-        <v>10.52119561557815</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.9010606955138831</v>
       </c>
       <c r="I79" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="J79" t="n">
-        <v>1.664668249059251</v>
+        <v>1.625040018662643</v>
       </c>
       <c r="K79" t="n">
-        <v>10.52119561557815</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="80">
@@ -3395,22 +3395,22 @@
         <v>177.9365297650131</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4027456965508756</v>
+        <v>0.770041370960776</v>
       </c>
       <c r="G80" t="n">
-        <v>11.97193061940716</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>0.9010606955138831</v>
       </c>
       <c r="I80" t="n">
         <v>177.9365297650131</v>
       </c>
       <c r="J80" t="n">
-        <v>1.664668249059251</v>
+        <v>1.625040018662643</v>
       </c>
       <c r="K80" t="n">
-        <v>11.97193061940716</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="81">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>13.09491170153377</v>
+        <v>177.9365297650131</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>13.09491170153377</v>
+        <v>177.9365297650131</v>
       </c>
     </row>
     <row r="82">
@@ -3470,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
